--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetAstBillInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetAstBillInfo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13125" tabRatio="743" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13125" tabRatio="743"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -4800,27 +4800,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4828,6 +4807,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4854,40 +4845,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4900,6 +4879,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4907,6 +4895,18 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5274,8 +5274,9 @@
     <col min="11" max="11" width="22" style="61" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" style="60" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22" style="60" customWidth="1"/>
-    <col min="14" max="15" width="8.875" style="62" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="62" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="62" customWidth="1"/>
+    <col min="16" max="16" width="14.625" style="49" customWidth="1"/>
     <col min="17" max="17" width="16.625" style="49" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.375" style="63" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17.625" style="49" bestFit="1" customWidth="1"/>
@@ -5576,7 +5577,7 @@
   <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="40">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="P1:Q1 AX3:AX65515 X3:X65515 S3:S65515 P3:Q65515"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="Q3:Q65515 X2 S2 P2 Q1 AX2"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不可为负，整数位不可超过13位，小数位不可超过2位" sqref="J1:J2">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
@@ -5615,7 +5616,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1">
       <formula1>"01 结构性投资类,02 债券类,03 股票类,04 股权类,05 另类投资类,06 混合类,07 非标准化债权类,08 银行存款类,09 理财直接融资工具类,10 新增可投资资产类,11 代客境外投资类,12 公募基金类,13 衍生产品类,14 商品类,15 同业存单类,16 拆放同业及买入返售类"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R3:R1048576">
+      <formula1>"01 是,02 否"</formula1>
+    </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65501">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
@@ -5718,7 +5721,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
@@ -5730,6 +5733,24 @@
             <xm:f>币种填写规则!$A$1:$A$178</xm:f>
           </x14:formula1>
           <xm:sqref>E1 E3:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
+          </x14:formula1>
+          <xm:sqref>P1 P3:P1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+          <x14:formula1>
+            <xm:f>国家或区域填写规则!$A$1:$A$239</xm:f>
+          </x14:formula1>
+          <xm:sqref>S1 S3:S1048576 X1 X3:X1048576 AX1 AX3:AX1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
+          </x14:formula1>
+          <xm:sqref>AL1 AL3:AL1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5799,13 +5820,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="86"/>
+      <c r="B1" s="104"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="94" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5813,25 +5834,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="98"/>
+      <c r="A3" s="95"/>
       <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="98"/>
+      <c r="A4" s="95"/>
       <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="99"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="97" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5839,13 +5860,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="101"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="99" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5853,13 +5874,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="101"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="100" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5867,61 +5888,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="103"/>
+      <c r="A11" s="101"/>
       <c r="B11" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="103"/>
+      <c r="A12" s="101"/>
       <c r="B12" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="103"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="103"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="103"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="103"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="103"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="103"/>
+      <c r="A18" s="101"/>
       <c r="B18" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="103"/>
+      <c r="A19" s="101"/>
       <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="103"/>
+      <c r="A20" s="101"/>
       <c r="B20" s="15" t="s">
         <v>53</v>
       </c>
@@ -5935,7 +5956,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="100" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5943,19 +5964,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="103"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="91"/>
+      <c r="A24" s="102"/>
       <c r="B24" s="13" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="100" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5963,67 +5984,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="103"/>
+      <c r="A26" s="101"/>
       <c r="B26" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="103"/>
+      <c r="A27" s="101"/>
       <c r="B27" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="103"/>
+      <c r="A28" s="101"/>
       <c r="B28" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="103"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="103"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="103"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="103"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="103"/>
+      <c r="A33" s="101"/>
       <c r="B33" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="103"/>
+      <c r="A34" s="101"/>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="91"/>
+      <c r="A35" s="102"/>
       <c r="B35" s="30" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="100" t="s">
         <v>72</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -6031,25 +6052,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="103"/>
+      <c r="A37" s="101"/>
       <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="103"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="91"/>
+      <c r="A39" s="102"/>
       <c r="B39" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="90" t="s">
+      <c r="A40" s="100" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -6057,43 +6078,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="103"/>
+      <c r="A41" s="101"/>
       <c r="B41" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="103"/>
+      <c r="A42" s="101"/>
       <c r="B42" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="103"/>
+      <c r="A43" s="101"/>
       <c r="B43" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="103"/>
+      <c r="A44" s="101"/>
       <c r="B44" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="103"/>
+      <c r="A45" s="101"/>
       <c r="B45" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="91"/>
+      <c r="A46" s="102"/>
       <c r="B46" s="13" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="90" t="s">
+      <c r="A47" s="100" t="s">
         <v>85</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -6101,61 +6122,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="103"/>
+      <c r="A48" s="101"/>
       <c r="B48" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="103"/>
+      <c r="A49" s="101"/>
       <c r="B49" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="103"/>
+      <c r="A50" s="101"/>
       <c r="B50" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="103"/>
+      <c r="A51" s="101"/>
       <c r="B51" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="103"/>
+      <c r="A52" s="101"/>
       <c r="B52" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="103"/>
+      <c r="A53" s="101"/>
       <c r="B53" s="15" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="103"/>
+      <c r="A54" s="101"/>
       <c r="B54" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="103"/>
+      <c r="A55" s="101"/>
       <c r="B55" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="91"/>
+      <c r="A56" s="102"/>
       <c r="B56" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="90" t="s">
+      <c r="A57" s="100" t="s">
         <v>96</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -6163,19 +6184,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="103"/>
+      <c r="A58" s="101"/>
       <c r="B58" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="91"/>
+      <c r="A59" s="102"/>
       <c r="B59" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="90" t="s">
+      <c r="A60" s="100" t="s">
         <v>100</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -6183,37 +6204,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="103"/>
+      <c r="A61" s="101"/>
       <c r="B61" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="103"/>
+      <c r="A62" s="101"/>
       <c r="B62" s="24" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="103"/>
+      <c r="A63" s="101"/>
       <c r="B63" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="103"/>
+      <c r="A64" s="101"/>
       <c r="B64" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="91"/>
+      <c r="A65" s="102"/>
       <c r="B65" s="17" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="90" t="s">
+      <c r="A66" s="100" t="s">
         <v>107</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -6221,37 +6242,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="103"/>
+      <c r="A67" s="101"/>
       <c r="B67" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="103"/>
+      <c r="A68" s="101"/>
       <c r="B68" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="103"/>
+      <c r="A69" s="101"/>
       <c r="B69" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="103"/>
+      <c r="A70" s="101"/>
       <c r="B70" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="91"/>
+      <c r="A71" s="102"/>
       <c r="B71" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="90" t="s">
+      <c r="A72" s="100" t="s">
         <v>114</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6259,103 +6280,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="103"/>
+      <c r="A73" s="101"/>
       <c r="B73" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="103"/>
+      <c r="A74" s="101"/>
       <c r="B74" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="103"/>
+      <c r="A75" s="101"/>
       <c r="B75" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="103"/>
+      <c r="A76" s="101"/>
       <c r="B76" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="103"/>
+      <c r="A77" s="101"/>
       <c r="B77" s="25" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="103"/>
+      <c r="A78" s="101"/>
       <c r="B78" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="103"/>
+      <c r="A79" s="101"/>
       <c r="B79" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="103"/>
+      <c r="A80" s="101"/>
       <c r="B80" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="103"/>
+      <c r="A81" s="101"/>
       <c r="B81" s="25" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="103"/>
+      <c r="A82" s="101"/>
       <c r="B82" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="103"/>
+      <c r="A83" s="101"/>
       <c r="B83" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="103"/>
+      <c r="A84" s="101"/>
       <c r="B84" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="103"/>
+      <c r="A85" s="101"/>
       <c r="B85" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="103"/>
+      <c r="A86" s="101"/>
       <c r="B86" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="103"/>
+      <c r="A87" s="101"/>
       <c r="B87" s="25" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="91"/>
+      <c r="A88" s="102"/>
       <c r="B88" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="90" t="s">
+      <c r="A89" s="100" t="s">
         <v>132</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6363,38 +6384,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="103"/>
+      <c r="A90" s="101"/>
       <c r="B90" s="15" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="103"/>
+      <c r="A91" s="101"/>
       <c r="B91" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="103"/>
+      <c r="A92" s="101"/>
       <c r="B92" s="32" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="103"/>
+      <c r="A93" s="101"/>
       <c r="B93" s="15" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="91"/>
+      <c r="A94" s="102"/>
       <c r="B94" s="13" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="90" t="s">
+      <c r="A95" s="100" t="s">
         <v>139</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6402,43 +6423,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="103"/>
+      <c r="A96" s="101"/>
       <c r="B96" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="103"/>
+      <c r="A97" s="101"/>
       <c r="B97" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="103"/>
+      <c r="A98" s="101"/>
       <c r="B98" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="103"/>
+      <c r="A99" s="101"/>
       <c r="B99" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="103"/>
+      <c r="A100" s="101"/>
       <c r="B100" s="25" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="91"/>
+      <c r="A101" s="102"/>
       <c r="B101" s="21" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="90" t="s">
+      <c r="A102" s="100" t="s">
         <v>147</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6446,7 +6467,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="91"/>
+      <c r="A103" s="102"/>
       <c r="B103" s="13" t="s">
         <v>149</v>
       </c>
@@ -6464,10 +6485,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="85" t="s">
+      <c r="A107" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="B107" s="86"/>
+      <c r="B107" s="104"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6638,17 +6659,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="104" t="s">
+      <c r="A137" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="B137" s="105"/>
+      <c r="B137" s="89"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="106"/>
-      <c r="B138" s="107"/>
+      <c r="A138" s="90"/>
+      <c r="B138" s="91"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="92" t="s">
+      <c r="A139" s="85" t="s">
         <v>182</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6656,31 +6677,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="93"/>
+      <c r="A140" s="86"/>
       <c r="B140" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="93"/>
+      <c r="A141" s="86"/>
       <c r="B141" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="93"/>
+      <c r="A142" s="86"/>
       <c r="B142" s="39" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="94"/>
+      <c r="A143" s="87"/>
       <c r="B143" s="41" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="92" t="s">
+      <c r="A144" s="85" t="s">
         <v>188</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6688,43 +6709,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="93"/>
+      <c r="A145" s="86"/>
       <c r="B145" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="93"/>
+      <c r="A146" s="86"/>
       <c r="B146" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="93"/>
+      <c r="A147" s="86"/>
       <c r="B147" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="93"/>
+      <c r="A148" s="86"/>
       <c r="B148" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="93"/>
+      <c r="A149" s="86"/>
       <c r="B149" s="39" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="94"/>
+      <c r="A150" s="87"/>
       <c r="B150" s="41" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="92" t="s">
+      <c r="A151" s="85" t="s">
         <v>196</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6732,187 +6753,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="93"/>
+      <c r="A152" s="86"/>
       <c r="B152" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="93"/>
+      <c r="A153" s="86"/>
       <c r="B153" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="93"/>
+      <c r="A154" s="86"/>
       <c r="B154" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="93"/>
+      <c r="A155" s="86"/>
       <c r="B155" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="93"/>
+      <c r="A156" s="86"/>
       <c r="B156" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="93"/>
+      <c r="A157" s="86"/>
       <c r="B157" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="93"/>
+      <c r="A158" s="86"/>
       <c r="B158" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="93"/>
+      <c r="A159" s="86"/>
       <c r="B159" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="93"/>
+      <c r="A160" s="86"/>
       <c r="B160" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="93"/>
+      <c r="A161" s="86"/>
       <c r="B161" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="93"/>
+      <c r="A162" s="86"/>
       <c r="B162" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="93"/>
+      <c r="A163" s="86"/>
       <c r="B163" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="93"/>
+      <c r="A164" s="86"/>
       <c r="B164" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="93"/>
+      <c r="A165" s="86"/>
       <c r="B165" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="93"/>
+      <c r="A166" s="86"/>
       <c r="B166" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="93"/>
+      <c r="A167" s="86"/>
       <c r="B167" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="93"/>
+      <c r="A168" s="86"/>
       <c r="B168" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="93"/>
+      <c r="A169" s="86"/>
       <c r="B169" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="93"/>
+      <c r="A170" s="86"/>
       <c r="B170" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="93"/>
+      <c r="A171" s="86"/>
       <c r="B171" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="93"/>
+      <c r="A172" s="86"/>
       <c r="B172" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="93"/>
+      <c r="A173" s="86"/>
       <c r="B173" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="93"/>
+      <c r="A174" s="86"/>
       <c r="B174" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="93"/>
+      <c r="A175" s="86"/>
       <c r="B175" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="93"/>
+      <c r="A176" s="86"/>
       <c r="B176" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="93"/>
+      <c r="A177" s="86"/>
       <c r="B177" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="93"/>
+      <c r="A178" s="86"/>
       <c r="B178" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="93"/>
+      <c r="A179" s="86"/>
       <c r="B179" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="93"/>
+      <c r="A180" s="86"/>
       <c r="B180" s="39" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="94"/>
+      <c r="A181" s="87"/>
       <c r="B181" s="41" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="92" t="s">
+      <c r="A182" s="85" t="s">
         <v>228</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6920,19 +6941,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="93"/>
+      <c r="A183" s="86"/>
       <c r="B183" s="39" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="94"/>
+      <c r="A184" s="87"/>
       <c r="B184" s="41" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="92" t="s">
+      <c r="A185" s="85" t="s">
         <v>232</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6940,25 +6961,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="93"/>
+      <c r="A186" s="86"/>
       <c r="B186" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="93"/>
+      <c r="A187" s="86"/>
       <c r="B187" s="39" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="94"/>
+      <c r="A188" s="87"/>
       <c r="B188" s="41" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="92" t="s">
+      <c r="A189" s="85" t="s">
         <v>237</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6966,13 +6987,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="94"/>
+      <c r="A190" s="87"/>
       <c r="B190" s="41" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="92" t="s">
+      <c r="A191" s="85" t="s">
         <v>240</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6980,49 +7001,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="93"/>
+      <c r="A192" s="86"/>
       <c r="B192" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="93"/>
+      <c r="A193" s="86"/>
       <c r="B193" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="93"/>
+      <c r="A194" s="86"/>
       <c r="B194" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="93"/>
+      <c r="A195" s="86"/>
       <c r="B195" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="93"/>
+      <c r="A196" s="86"/>
       <c r="B196" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="93"/>
+      <c r="A197" s="86"/>
       <c r="B197" s="39" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="94"/>
+      <c r="A198" s="87"/>
       <c r="B198" s="41" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="92" t="s">
+      <c r="A199" s="85" t="s">
         <v>249</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -7030,13 +7051,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="94"/>
+      <c r="A200" s="87"/>
       <c r="B200" s="41" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="92" t="s">
+      <c r="A201" s="85" t="s">
         <v>252</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -7044,19 +7065,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="93"/>
+      <c r="A202" s="86"/>
       <c r="B202" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="94"/>
+      <c r="A203" s="87"/>
       <c r="B203" s="41" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="92" t="s">
+      <c r="A204" s="85" t="s">
         <v>256</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -7064,19 +7085,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="93"/>
+      <c r="A205" s="86"/>
       <c r="B205" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="93"/>
+      <c r="A206" s="86"/>
       <c r="B206" s="39" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="94"/>
+      <c r="A207" s="87"/>
       <c r="B207" s="41" t="s">
         <v>260</v>
       </c>
@@ -7090,7 +7111,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="92" t="s">
+      <c r="A209" s="85" t="s">
         <v>263</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -7098,13 +7119,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="94"/>
+      <c r="A210" s="87"/>
       <c r="B210" s="41" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="92" t="s">
+      <c r="A211" s="85" t="s">
         <v>266</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -7112,19 +7133,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="93"/>
+      <c r="A212" s="86"/>
       <c r="B212" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="94"/>
+      <c r="A213" s="87"/>
       <c r="B213" s="41" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="92" t="s">
+      <c r="A214" s="85" t="s">
         <v>270</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -7132,19 +7153,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="93"/>
+      <c r="A215" s="86"/>
       <c r="B215" s="39" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="94"/>
+      <c r="A216" s="87"/>
       <c r="B216" s="41" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="92" t="s">
+      <c r="A217" s="85" t="s">
         <v>274</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -7152,13 +7173,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="93"/>
+      <c r="A218" s="86"/>
       <c r="B218" s="39" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="94"/>
+      <c r="A219" s="87"/>
       <c r="B219" s="41" t="s">
         <v>277</v>
       </c>
@@ -7172,7 +7193,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="92" t="s">
+      <c r="A221" s="85" t="s">
         <v>280</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -7180,13 +7201,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="94"/>
+      <c r="A222" s="87"/>
       <c r="B222" s="41" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="92" t="s">
+      <c r="A223" s="85" t="s">
         <v>283</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -7194,31 +7215,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="93"/>
+      <c r="A224" s="86"/>
       <c r="B224" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="93"/>
+      <c r="A225" s="86"/>
       <c r="B225" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="93"/>
+      <c r="A226" s="86"/>
       <c r="B226" s="39" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="94"/>
+      <c r="A227" s="87"/>
       <c r="B227" s="41" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="92" t="s">
+      <c r="A228" s="85" t="s">
         <v>289</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7226,31 +7247,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="93"/>
+      <c r="A229" s="86"/>
       <c r="B229" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="93"/>
+      <c r="A230" s="86"/>
       <c r="B230" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="93"/>
+      <c r="A231" s="86"/>
       <c r="B231" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="93"/>
+      <c r="A232" s="86"/>
       <c r="B232" s="39" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="94"/>
+      <c r="A233" s="87"/>
       <c r="B233" s="41" t="s">
         <v>295</v>
       </c>
@@ -7264,16 +7285,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="87" t="s">
+      <c r="A236" s="105" t="s">
         <v>298</v>
       </c>
-      <c r="B236" s="86"/>
+      <c r="B236" s="104"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="85" t="s">
+      <c r="A239" s="103" t="s">
         <v>299</v>
       </c>
-      <c r="B239" s="86"/>
+      <c r="B239" s="104"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7372,10 +7393,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="88" t="s">
+      <c r="A257" s="106" t="s">
         <v>316</v>
       </c>
-      <c r="B257" s="89"/>
+      <c r="B257" s="107"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7552,10 +7573,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="95" t="s">
+      <c r="A288" s="92" t="s">
         <v>346</v>
       </c>
-      <c r="B288" s="96"/>
+      <c r="B288" s="93"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7746,14 +7767,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7770,22 +7799,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7805,10 +7826,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="117" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="109"/>
+      <c r="B1" s="118"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7822,7 +7843,7 @@
       <c r="A3" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7830,25 +7851,25 @@
       <c r="A4" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="111"/>
+      <c r="B4" s="112"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="111"/>
+      <c r="B5" s="112"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="112"/>
+      <c r="B6" s="113"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="111" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7856,25 +7877,25 @@
       <c r="A8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="111"/>
+      <c r="B8" s="112"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="111"/>
+      <c r="B9" s="112"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="112"/>
+      <c r="B10" s="113"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="111" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7882,85 +7903,85 @@
       <c r="A12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="111"/>
+      <c r="B12" s="112"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="111"/>
+      <c r="B13" s="112"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="111"/>
+      <c r="B14" s="112"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="111"/>
+      <c r="B15" s="112"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="111"/>
+      <c r="B16" s="112"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="111"/>
+      <c r="B17" s="112"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B18" s="111"/>
+      <c r="B18" s="112"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="111"/>
+      <c r="B19" s="112"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="B20" s="111"/>
+      <c r="B20" s="112"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="B21" s="111"/>
+      <c r="B21" s="112"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="111"/>
+      <c r="B22" s="112"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="113"/>
+      <c r="B23" s="119"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="114"/>
+      <c r="B24" s="120"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="111" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7968,61 +7989,61 @@
       <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="111"/>
+      <c r="B26" s="112"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="111"/>
+      <c r="B27" s="112"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="111"/>
+      <c r="B28" s="112"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="111"/>
+      <c r="B29" s="112"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B30" s="111"/>
+      <c r="B30" s="112"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="111"/>
+      <c r="B31" s="112"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B32" s="111"/>
+      <c r="B32" s="112"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B33" s="111"/>
+      <c r="B33" s="112"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="112"/>
+      <c r="B34" s="113"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="111" t="s">
         <v>392</v>
       </c>
     </row>
@@ -8030,13 +8051,13 @@
       <c r="A36" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B36" s="112"/>
+      <c r="B36" s="113"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="110" t="s">
+      <c r="B37" s="111" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8044,19 +8065,19 @@
       <c r="A38" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="111"/>
+      <c r="B38" s="112"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="111"/>
+      <c r="B39" s="112"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B40" s="110" t="s">
+      <c r="B40" s="111" t="s">
         <v>395</v>
       </c>
     </row>
@@ -8064,37 +8085,37 @@
       <c r="A41" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B41" s="111"/>
+      <c r="B41" s="112"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="111"/>
+      <c r="B42" s="112"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B43" s="111"/>
+      <c r="B43" s="112"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="B44" s="111"/>
+      <c r="B44" s="112"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="111"/>
+      <c r="B45" s="112"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="112"/>
+      <c r="B46" s="113"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -8108,7 +8129,7 @@
       <c r="A48" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="110" t="s">
+      <c r="B48" s="111" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8116,13 +8137,13 @@
       <c r="A49" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="112"/>
+      <c r="B49" s="113"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="110" t="s">
+      <c r="B50" s="111" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8130,25 +8151,25 @@
       <c r="A51" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="111"/>
+      <c r="B51" s="112"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B52" s="111"/>
+      <c r="B52" s="112"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="111"/>
+      <c r="B53" s="112"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="112"/>
+      <c r="B54" s="113"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -8162,7 +8183,7 @@
       <c r="A56" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B56" s="110" t="s">
+      <c r="B56" s="111" t="s">
         <v>8</v>
       </c>
     </row>
@@ -8170,19 +8191,19 @@
       <c r="A57" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="111"/>
+      <c r="B57" s="112"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="112"/>
+      <c r="B58" s="113"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B59" s="110" t="s">
+      <c r="B59" s="111" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8190,37 +8211,37 @@
       <c r="A60" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="111"/>
+      <c r="B60" s="112"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="111"/>
+      <c r="B61" s="112"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="111"/>
+      <c r="B62" s="112"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="111"/>
+      <c r="B63" s="112"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B64" s="112"/>
+      <c r="B64" s="113"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B65" s="118" t="s">
+      <c r="B65" s="114" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8228,26 +8249,26 @@
       <c r="A66" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="119"/>
+      <c r="B66" s="115"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B67" s="119"/>
+      <c r="B67" s="115"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B68" s="120"/>
+      <c r="B68" s="116"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="110" t="s">
+      <c r="B69" s="111" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8255,37 +8276,37 @@
       <c r="A70" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B70" s="111"/>
+      <c r="B70" s="112"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B71" s="111"/>
+      <c r="B71" s="112"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B72" s="111"/>
+      <c r="B72" s="112"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B73" s="111"/>
+      <c r="B73" s="112"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B74" s="112"/>
+      <c r="B74" s="113"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B75" s="110" t="s">
+      <c r="B75" s="111" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8293,139 +8314,139 @@
       <c r="A76" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B76" s="111"/>
+      <c r="B76" s="112"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="111"/>
+      <c r="B77" s="112"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B78" s="111"/>
+      <c r="B78" s="112"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B79" s="111"/>
+      <c r="B79" s="112"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B80" s="111"/>
+      <c r="B80" s="112"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B81" s="111"/>
+      <c r="B81" s="112"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B82" s="111"/>
+      <c r="B82" s="112"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B83" s="111"/>
+      <c r="B83" s="112"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="111"/>
+      <c r="B84" s="112"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B85" s="111"/>
+      <c r="B85" s="112"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B86" s="111"/>
+      <c r="B86" s="112"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B87" s="111"/>
+      <c r="B87" s="112"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="111"/>
+      <c r="B88" s="112"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B89" s="111"/>
+      <c r="B89" s="112"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B90" s="111"/>
+      <c r="B90" s="112"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B91" s="111"/>
+      <c r="B91" s="112"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B92" s="111"/>
+      <c r="B92" s="112"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B93" s="111"/>
+      <c r="B93" s="112"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="111"/>
+      <c r="B94" s="112"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B95" s="111"/>
+      <c r="B95" s="112"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B96" s="111"/>
+      <c r="B96" s="112"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="111"/>
+      <c r="B97" s="112"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="B98" s="115" t="s">
+      <c r="B98" s="108" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8433,37 +8454,37 @@
       <c r="A99" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B99" s="116"/>
+      <c r="B99" s="109"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B100" s="116"/>
+      <c r="B100" s="109"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B101" s="116"/>
+      <c r="B101" s="109"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B102" s="116"/>
+      <c r="B102" s="109"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B103" s="116"/>
+      <c r="B103" s="109"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B104" s="117"/>
+      <c r="B104" s="110"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8475,22 +8496,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetAstBillInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetAstBillInfo.xlsx
@@ -4800,6 +4800,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4807,18 +4828,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4845,28 +4854,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4879,15 +4900,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4895,18 +4907,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5697,9 +5697,6 @@
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO3:AO65515">
-      <formula1>"01 集合管理,02 专户管理,99 其他"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最高收益率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AQ3:AQ1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
@@ -5716,6 +5713,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C1 C3:C1048576">
       <formula1>"1201 票据类  ,1210 信用证,1601 贵金属类,1602 大宗商品类,1699 其他商品类资产,2301 字画类艺术品,2302 古董类艺术品,2303 其他类艺术品,2304 影视等知识产权,2305 酒,1603 其他另类资产,2801 协议委外-银行,2802 协议委外-信托公司,2803 协议委外-证券公司,2804 协议委外-基金公司,2805 协议委外-期货公司,2806 协议委外-保险公司,2899 协议委外-其他,2000 其他(负债)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1 AO3:AO1048576">
+      <formula1>"01 集合管理,02 单独管理,99 其他"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
@@ -5820,13 +5820,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="104"/>
+      <c r="B1" s="86"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="97" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5834,25 +5834,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="95"/>
+      <c r="A3" s="98"/>
       <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="95"/>
+      <c r="A4" s="98"/>
       <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="96"/>
+      <c r="A5" s="99"/>
       <c r="B5" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="100" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5860,13 +5860,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="98"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="99" t="s">
+      <c r="A8" s="102" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5874,13 +5874,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="98"/>
+      <c r="A9" s="101"/>
       <c r="B9" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="90" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5888,61 +5888,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="101"/>
+      <c r="A11" s="103"/>
       <c r="B11" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="101"/>
+      <c r="A12" s="103"/>
       <c r="B12" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="101"/>
+      <c r="A13" s="103"/>
       <c r="B13" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="101"/>
+      <c r="A14" s="103"/>
       <c r="B14" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="101"/>
+      <c r="A15" s="103"/>
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="101"/>
+      <c r="A16" s="103"/>
       <c r="B16" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="101"/>
+      <c r="A17" s="103"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="101"/>
+      <c r="A18" s="103"/>
       <c r="B18" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="101"/>
+      <c r="A19" s="103"/>
       <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="101"/>
+      <c r="A20" s="103"/>
       <c r="B20" s="15" t="s">
         <v>53</v>
       </c>
@@ -5956,7 +5956,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="90" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5964,19 +5964,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="101"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="102"/>
+      <c r="A24" s="91"/>
       <c r="B24" s="13" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="90" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5984,67 +5984,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="101"/>
+      <c r="A26" s="103"/>
       <c r="B26" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="101"/>
+      <c r="A27" s="103"/>
       <c r="B27" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="101"/>
+      <c r="A28" s="103"/>
       <c r="B28" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="101"/>
+      <c r="A29" s="103"/>
       <c r="B29" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="101"/>
+      <c r="A30" s="103"/>
       <c r="B30" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="101"/>
+      <c r="A31" s="103"/>
       <c r="B31" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="101"/>
+      <c r="A32" s="103"/>
       <c r="B32" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="101"/>
+      <c r="A33" s="103"/>
       <c r="B33" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="101"/>
+      <c r="A34" s="103"/>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="102"/>
+      <c r="A35" s="91"/>
       <c r="B35" s="30" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="100" t="s">
+      <c r="A36" s="90" t="s">
         <v>72</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -6052,25 +6052,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="101"/>
+      <c r="A37" s="103"/>
       <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="101"/>
+      <c r="A38" s="103"/>
       <c r="B38" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="102"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="100" t="s">
+      <c r="A40" s="90" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -6078,43 +6078,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="101"/>
+      <c r="A41" s="103"/>
       <c r="B41" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="101"/>
+      <c r="A42" s="103"/>
       <c r="B42" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="101"/>
+      <c r="A43" s="103"/>
       <c r="B43" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="101"/>
+      <c r="A44" s="103"/>
       <c r="B44" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="101"/>
+      <c r="A45" s="103"/>
       <c r="B45" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="102"/>
+      <c r="A46" s="91"/>
       <c r="B46" s="13" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="100" t="s">
+      <c r="A47" s="90" t="s">
         <v>85</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -6122,61 +6122,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="101"/>
+      <c r="A48" s="103"/>
       <c r="B48" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="101"/>
+      <c r="A49" s="103"/>
       <c r="B49" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="101"/>
+      <c r="A50" s="103"/>
       <c r="B50" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="101"/>
+      <c r="A51" s="103"/>
       <c r="B51" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="101"/>
+      <c r="A52" s="103"/>
       <c r="B52" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="101"/>
+      <c r="A53" s="103"/>
       <c r="B53" s="15" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="101"/>
+      <c r="A54" s="103"/>
       <c r="B54" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="101"/>
+      <c r="A55" s="103"/>
       <c r="B55" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="102"/>
+      <c r="A56" s="91"/>
       <c r="B56" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="100" t="s">
+      <c r="A57" s="90" t="s">
         <v>96</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -6184,19 +6184,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="101"/>
+      <c r="A58" s="103"/>
       <c r="B58" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="102"/>
+      <c r="A59" s="91"/>
       <c r="B59" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="100" t="s">
+      <c r="A60" s="90" t="s">
         <v>100</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -6204,37 +6204,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="101"/>
+      <c r="A61" s="103"/>
       <c r="B61" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="101"/>
+      <c r="A62" s="103"/>
       <c r="B62" s="24" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="101"/>
+      <c r="A63" s="103"/>
       <c r="B63" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="101"/>
+      <c r="A64" s="103"/>
       <c r="B64" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="102"/>
+      <c r="A65" s="91"/>
       <c r="B65" s="17" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="100" t="s">
+      <c r="A66" s="90" t="s">
         <v>107</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -6242,37 +6242,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="101"/>
+      <c r="A67" s="103"/>
       <c r="B67" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="101"/>
+      <c r="A68" s="103"/>
       <c r="B68" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="101"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="101"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="102"/>
+      <c r="A71" s="91"/>
       <c r="B71" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="100" t="s">
+      <c r="A72" s="90" t="s">
         <v>114</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6280,103 +6280,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="101"/>
+      <c r="A73" s="103"/>
       <c r="B73" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="101"/>
+      <c r="A74" s="103"/>
       <c r="B74" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="101"/>
+      <c r="A75" s="103"/>
       <c r="B75" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="101"/>
+      <c r="A76" s="103"/>
       <c r="B76" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="101"/>
+      <c r="A77" s="103"/>
       <c r="B77" s="25" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="101"/>
+      <c r="A78" s="103"/>
       <c r="B78" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="101"/>
+      <c r="A79" s="103"/>
       <c r="B79" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="101"/>
+      <c r="A80" s="103"/>
       <c r="B80" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="101"/>
+      <c r="A81" s="103"/>
       <c r="B81" s="25" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="101"/>
+      <c r="A82" s="103"/>
       <c r="B82" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="101"/>
+      <c r="A83" s="103"/>
       <c r="B83" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="101"/>
+      <c r="A84" s="103"/>
       <c r="B84" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="101"/>
+      <c r="A85" s="103"/>
       <c r="B85" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="101"/>
+      <c r="A86" s="103"/>
       <c r="B86" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="101"/>
+      <c r="A87" s="103"/>
       <c r="B87" s="25" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="102"/>
+      <c r="A88" s="91"/>
       <c r="B88" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="100" t="s">
+      <c r="A89" s="90" t="s">
         <v>132</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6384,38 +6384,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="101"/>
+      <c r="A90" s="103"/>
       <c r="B90" s="15" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="101"/>
+      <c r="A91" s="103"/>
       <c r="B91" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="101"/>
+      <c r="A92" s="103"/>
       <c r="B92" s="32" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="101"/>
+      <c r="A93" s="103"/>
       <c r="B93" s="15" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="102"/>
+      <c r="A94" s="91"/>
       <c r="B94" s="13" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="100" t="s">
+      <c r="A95" s="90" t="s">
         <v>139</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6423,43 +6423,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="101"/>
+      <c r="A96" s="103"/>
       <c r="B96" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="101"/>
+      <c r="A97" s="103"/>
       <c r="B97" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="101"/>
+      <c r="A98" s="103"/>
       <c r="B98" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="101"/>
+      <c r="A99" s="103"/>
       <c r="B99" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="101"/>
+      <c r="A100" s="103"/>
       <c r="B100" s="25" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="102"/>
+      <c r="A101" s="91"/>
       <c r="B101" s="21" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="100" t="s">
+      <c r="A102" s="90" t="s">
         <v>147</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6467,7 +6467,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="102"/>
+      <c r="A103" s="91"/>
       <c r="B103" s="13" t="s">
         <v>149</v>
       </c>
@@ -6485,10 +6485,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="103" t="s">
+      <c r="A107" s="85" t="s">
         <v>152</v>
       </c>
-      <c r="B107" s="104"/>
+      <c r="B107" s="86"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6659,17 +6659,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="88" t="s">
+      <c r="A137" s="104" t="s">
         <v>181</v>
       </c>
-      <c r="B137" s="89"/>
+      <c r="B137" s="105"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="90"/>
-      <c r="B138" s="91"/>
+      <c r="A138" s="106"/>
+      <c r="B138" s="107"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="85" t="s">
+      <c r="A139" s="92" t="s">
         <v>182</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6677,31 +6677,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="86"/>
+      <c r="A140" s="93"/>
       <c r="B140" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="86"/>
+      <c r="A141" s="93"/>
       <c r="B141" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="86"/>
+      <c r="A142" s="93"/>
       <c r="B142" s="39" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="87"/>
+      <c r="A143" s="94"/>
       <c r="B143" s="41" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="85" t="s">
+      <c r="A144" s="92" t="s">
         <v>188</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6709,43 +6709,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="86"/>
+      <c r="A145" s="93"/>
       <c r="B145" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="86"/>
+      <c r="A146" s="93"/>
       <c r="B146" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="86"/>
+      <c r="A147" s="93"/>
       <c r="B147" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="86"/>
+      <c r="A148" s="93"/>
       <c r="B148" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="86"/>
+      <c r="A149" s="93"/>
       <c r="B149" s="39" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="87"/>
+      <c r="A150" s="94"/>
       <c r="B150" s="41" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="85" t="s">
+      <c r="A151" s="92" t="s">
         <v>196</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6753,187 +6753,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="86"/>
+      <c r="A152" s="93"/>
       <c r="B152" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="86"/>
+      <c r="A153" s="93"/>
       <c r="B153" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="86"/>
+      <c r="A154" s="93"/>
       <c r="B154" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="86"/>
+      <c r="A155" s="93"/>
       <c r="B155" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="86"/>
+      <c r="A156" s="93"/>
       <c r="B156" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="86"/>
+      <c r="A157" s="93"/>
       <c r="B157" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="86"/>
+      <c r="A158" s="93"/>
       <c r="B158" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="86"/>
+      <c r="A159" s="93"/>
       <c r="B159" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="86"/>
+      <c r="A160" s="93"/>
       <c r="B160" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="86"/>
+      <c r="A161" s="93"/>
       <c r="B161" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="86"/>
+      <c r="A162" s="93"/>
       <c r="B162" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="86"/>
+      <c r="A163" s="93"/>
       <c r="B163" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="86"/>
+      <c r="A164" s="93"/>
       <c r="B164" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="86"/>
+      <c r="A165" s="93"/>
       <c r="B165" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="86"/>
+      <c r="A166" s="93"/>
       <c r="B166" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="86"/>
+      <c r="A167" s="93"/>
       <c r="B167" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="86"/>
+      <c r="A168" s="93"/>
       <c r="B168" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="86"/>
+      <c r="A169" s="93"/>
       <c r="B169" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="86"/>
+      <c r="A170" s="93"/>
       <c r="B170" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="86"/>
+      <c r="A171" s="93"/>
       <c r="B171" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="86"/>
+      <c r="A172" s="93"/>
       <c r="B172" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="86"/>
+      <c r="A173" s="93"/>
       <c r="B173" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="86"/>
+      <c r="A174" s="93"/>
       <c r="B174" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="86"/>
+      <c r="A175" s="93"/>
       <c r="B175" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="86"/>
+      <c r="A176" s="93"/>
       <c r="B176" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="86"/>
+      <c r="A177" s="93"/>
       <c r="B177" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="86"/>
+      <c r="A178" s="93"/>
       <c r="B178" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="86"/>
+      <c r="A179" s="93"/>
       <c r="B179" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="86"/>
+      <c r="A180" s="93"/>
       <c r="B180" s="39" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="87"/>
+      <c r="A181" s="94"/>
       <c r="B181" s="41" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="85" t="s">
+      <c r="A182" s="92" t="s">
         <v>228</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6941,19 +6941,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="86"/>
+      <c r="A183" s="93"/>
       <c r="B183" s="39" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="87"/>
+      <c r="A184" s="94"/>
       <c r="B184" s="41" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="85" t="s">
+      <c r="A185" s="92" t="s">
         <v>232</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6961,25 +6961,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="86"/>
+      <c r="A186" s="93"/>
       <c r="B186" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="86"/>
+      <c r="A187" s="93"/>
       <c r="B187" s="39" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="87"/>
+      <c r="A188" s="94"/>
       <c r="B188" s="41" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="85" t="s">
+      <c r="A189" s="92" t="s">
         <v>237</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6987,13 +6987,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="87"/>
+      <c r="A190" s="94"/>
       <c r="B190" s="41" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="85" t="s">
+      <c r="A191" s="92" t="s">
         <v>240</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -7001,49 +7001,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="86"/>
+      <c r="A192" s="93"/>
       <c r="B192" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="86"/>
+      <c r="A193" s="93"/>
       <c r="B193" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="86"/>
+      <c r="A194" s="93"/>
       <c r="B194" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="86"/>
+      <c r="A195" s="93"/>
       <c r="B195" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="86"/>
+      <c r="A196" s="93"/>
       <c r="B196" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="86"/>
+      <c r="A197" s="93"/>
       <c r="B197" s="39" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="87"/>
+      <c r="A198" s="94"/>
       <c r="B198" s="41" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="85" t="s">
+      <c r="A199" s="92" t="s">
         <v>249</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -7051,13 +7051,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="87"/>
+      <c r="A200" s="94"/>
       <c r="B200" s="41" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="85" t="s">
+      <c r="A201" s="92" t="s">
         <v>252</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -7065,19 +7065,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="86"/>
+      <c r="A202" s="93"/>
       <c r="B202" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="87"/>
+      <c r="A203" s="94"/>
       <c r="B203" s="41" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="85" t="s">
+      <c r="A204" s="92" t="s">
         <v>256</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -7085,19 +7085,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="86"/>
+      <c r="A205" s="93"/>
       <c r="B205" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="86"/>
+      <c r="A206" s="93"/>
       <c r="B206" s="39" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="87"/>
+      <c r="A207" s="94"/>
       <c r="B207" s="41" t="s">
         <v>260</v>
       </c>
@@ -7111,7 +7111,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="85" t="s">
+      <c r="A209" s="92" t="s">
         <v>263</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -7119,13 +7119,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="87"/>
+      <c r="A210" s="94"/>
       <c r="B210" s="41" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="85" t="s">
+      <c r="A211" s="92" t="s">
         <v>266</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -7133,19 +7133,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="86"/>
+      <c r="A212" s="93"/>
       <c r="B212" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="87"/>
+      <c r="A213" s="94"/>
       <c r="B213" s="41" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="85" t="s">
+      <c r="A214" s="92" t="s">
         <v>270</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -7153,19 +7153,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="86"/>
+      <c r="A215" s="93"/>
       <c r="B215" s="39" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="87"/>
+      <c r="A216" s="94"/>
       <c r="B216" s="41" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="85" t="s">
+      <c r="A217" s="92" t="s">
         <v>274</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -7173,13 +7173,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="86"/>
+      <c r="A218" s="93"/>
       <c r="B218" s="39" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="87"/>
+      <c r="A219" s="94"/>
       <c r="B219" s="41" t="s">
         <v>277</v>
       </c>
@@ -7193,7 +7193,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="85" t="s">
+      <c r="A221" s="92" t="s">
         <v>280</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -7201,13 +7201,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="87"/>
+      <c r="A222" s="94"/>
       <c r="B222" s="41" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="85" t="s">
+      <c r="A223" s="92" t="s">
         <v>283</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -7215,31 +7215,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="86"/>
+      <c r="A224" s="93"/>
       <c r="B224" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="86"/>
+      <c r="A225" s="93"/>
       <c r="B225" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="86"/>
+      <c r="A226" s="93"/>
       <c r="B226" s="39" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="87"/>
+      <c r="A227" s="94"/>
       <c r="B227" s="41" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="85" t="s">
+      <c r="A228" s="92" t="s">
         <v>289</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7247,31 +7247,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="86"/>
+      <c r="A229" s="93"/>
       <c r="B229" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="86"/>
+      <c r="A230" s="93"/>
       <c r="B230" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="86"/>
+      <c r="A231" s="93"/>
       <c r="B231" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="86"/>
+      <c r="A232" s="93"/>
       <c r="B232" s="39" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="87"/>
+      <c r="A233" s="94"/>
       <c r="B233" s="41" t="s">
         <v>295</v>
       </c>
@@ -7285,16 +7285,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="105" t="s">
+      <c r="A236" s="87" t="s">
         <v>298</v>
       </c>
-      <c r="B236" s="104"/>
+      <c r="B236" s="86"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="103" t="s">
+      <c r="A239" s="85" t="s">
         <v>299</v>
       </c>
-      <c r="B239" s="104"/>
+      <c r="B239" s="86"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7393,10 +7393,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="106" t="s">
+      <c r="A257" s="88" t="s">
         <v>316</v>
       </c>
-      <c r="B257" s="107"/>
+      <c r="B257" s="89"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7573,10 +7573,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="92" t="s">
+      <c r="A288" s="95" t="s">
         <v>346</v>
       </c>
-      <c r="B288" s="93"/>
+      <c r="B288" s="96"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7767,6 +7767,30 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -7783,30 +7807,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7826,10 +7826,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="108" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="118"/>
+      <c r="B1" s="109"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7843,7 +7843,7 @@
       <c r="A3" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="110" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7851,25 +7851,25 @@
       <c r="A4" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="112"/>
+      <c r="B4" s="111"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="112"/>
+      <c r="B5" s="111"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="113"/>
+      <c r="B6" s="112"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="111" t="s">
+      <c r="B7" s="110" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7877,25 +7877,25 @@
       <c r="A8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="112"/>
+      <c r="B8" s="111"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="112"/>
+      <c r="B9" s="111"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="113"/>
+      <c r="B10" s="112"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="111" t="s">
+      <c r="B11" s="110" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7903,85 +7903,85 @@
       <c r="A12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="112"/>
+      <c r="B12" s="111"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="112"/>
+      <c r="B13" s="111"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="112"/>
+      <c r="B14" s="111"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="112"/>
+      <c r="B15" s="111"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="112"/>
+      <c r="B16" s="111"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="112"/>
+      <c r="B17" s="111"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B18" s="112"/>
+      <c r="B18" s="111"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="112"/>
+      <c r="B19" s="111"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="B20" s="112"/>
+      <c r="B20" s="111"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="B21" s="112"/>
+      <c r="B21" s="111"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="112"/>
+      <c r="B22" s="111"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="119"/>
+      <c r="B23" s="113"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="120"/>
+      <c r="B24" s="114"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B25" s="111" t="s">
+      <c r="B25" s="110" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7989,61 +7989,61 @@
       <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="112"/>
+      <c r="B26" s="111"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="112"/>
+      <c r="B27" s="111"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="112"/>
+      <c r="B28" s="111"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="112"/>
+      <c r="B29" s="111"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B30" s="112"/>
+      <c r="B30" s="111"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="112"/>
+      <c r="B31" s="111"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B32" s="112"/>
+      <c r="B32" s="111"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B33" s="112"/>
+      <c r="B33" s="111"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="113"/>
+      <c r="B34" s="112"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="B35" s="111" t="s">
+      <c r="B35" s="110" t="s">
         <v>392</v>
       </c>
     </row>
@@ -8051,13 +8051,13 @@
       <c r="A36" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B36" s="113"/>
+      <c r="B36" s="112"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="111" t="s">
+      <c r="B37" s="110" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8065,19 +8065,19 @@
       <c r="A38" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="112"/>
+      <c r="B38" s="111"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="112"/>
+      <c r="B39" s="111"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B40" s="111" t="s">
+      <c r="B40" s="110" t="s">
         <v>395</v>
       </c>
     </row>
@@ -8085,37 +8085,37 @@
       <c r="A41" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B41" s="112"/>
+      <c r="B41" s="111"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="112"/>
+      <c r="B42" s="111"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B43" s="112"/>
+      <c r="B43" s="111"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="B44" s="112"/>
+      <c r="B44" s="111"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="112"/>
+      <c r="B45" s="111"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="113"/>
+      <c r="B46" s="112"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -8129,7 +8129,7 @@
       <c r="A48" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="111" t="s">
+      <c r="B48" s="110" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8137,13 +8137,13 @@
       <c r="A49" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="113"/>
+      <c r="B49" s="112"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="111" t="s">
+      <c r="B50" s="110" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8151,25 +8151,25 @@
       <c r="A51" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="112"/>
+      <c r="B51" s="111"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B52" s="112"/>
+      <c r="B52" s="111"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="112"/>
+      <c r="B53" s="111"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="113"/>
+      <c r="B54" s="112"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -8183,7 +8183,7 @@
       <c r="A56" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B56" s="111" t="s">
+      <c r="B56" s="110" t="s">
         <v>8</v>
       </c>
     </row>
@@ -8191,19 +8191,19 @@
       <c r="A57" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="112"/>
+      <c r="B57" s="111"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="113"/>
+      <c r="B58" s="112"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B59" s="111" t="s">
+      <c r="B59" s="110" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8211,37 +8211,37 @@
       <c r="A60" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="112"/>
+      <c r="B60" s="111"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="112"/>
+      <c r="B61" s="111"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="112"/>
+      <c r="B62" s="111"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="112"/>
+      <c r="B63" s="111"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B64" s="113"/>
+      <c r="B64" s="112"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B65" s="114" t="s">
+      <c r="B65" s="118" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8249,26 +8249,26 @@
       <c r="A66" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="115"/>
+      <c r="B66" s="119"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B67" s="115"/>
+      <c r="B67" s="119"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B68" s="116"/>
+      <c r="B68" s="120"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="111" t="s">
+      <c r="B69" s="110" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8276,37 +8276,37 @@
       <c r="A70" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B70" s="112"/>
+      <c r="B70" s="111"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B71" s="112"/>
+      <c r="B71" s="111"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B72" s="112"/>
+      <c r="B72" s="111"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B73" s="112"/>
+      <c r="B73" s="111"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B74" s="113"/>
+      <c r="B74" s="112"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B75" s="111" t="s">
+      <c r="B75" s="110" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8314,139 +8314,139 @@
       <c r="A76" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B76" s="112"/>
+      <c r="B76" s="111"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="112"/>
+      <c r="B77" s="111"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B78" s="112"/>
+      <c r="B78" s="111"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B79" s="112"/>
+      <c r="B79" s="111"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B80" s="112"/>
+      <c r="B80" s="111"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B81" s="112"/>
+      <c r="B81" s="111"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B82" s="112"/>
+      <c r="B82" s="111"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B83" s="112"/>
+      <c r="B83" s="111"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="112"/>
+      <c r="B84" s="111"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B85" s="112"/>
+      <c r="B85" s="111"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B86" s="112"/>
+      <c r="B86" s="111"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B87" s="112"/>
+      <c r="B87" s="111"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="112"/>
+      <c r="B88" s="111"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B89" s="112"/>
+      <c r="B89" s="111"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B90" s="112"/>
+      <c r="B90" s="111"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B91" s="112"/>
+      <c r="B91" s="111"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B92" s="112"/>
+      <c r="B92" s="111"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B93" s="112"/>
+      <c r="B93" s="111"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="112"/>
+      <c r="B94" s="111"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B95" s="112"/>
+      <c r="B95" s="111"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B96" s="112"/>
+      <c r="B96" s="111"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="112"/>
+      <c r="B97" s="111"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="B98" s="108" t="s">
+      <c r="B98" s="115" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8454,37 +8454,37 @@
       <c r="A99" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B99" s="109"/>
+      <c r="B99" s="116"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B100" s="109"/>
+      <c r="B100" s="116"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B101" s="109"/>
+      <c r="B101" s="116"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B102" s="109"/>
+      <c r="B102" s="116"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B103" s="109"/>
+      <c r="B103" s="116"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B104" s="110"/>
+      <c r="B104" s="117"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8496,22 +8496,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetAstBillInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussRepAssetAstBillInfo.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="952">
   <si>
     <t>公共信息（必填）</t>
   </si>
@@ -4066,6 +4066,14 @@
   </si>
   <si>
     <t>ZWE 津巴布韦</t>
+  </si>
+  <si>
+    <t>*公共PPP</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>*是否投向市场化债转股相关产品的部分</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4800,27 +4808,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4828,6 +4815,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4854,40 +4853,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4900,6 +4887,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4907,6 +4903,18 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5258,7 +5266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF2"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.75" style="49" customWidth="1"/>
@@ -5278,43 +5286,45 @@
     <col min="15" max="15" width="12.5" style="62" customWidth="1"/>
     <col min="16" max="16" width="14.625" style="49" customWidth="1"/>
     <col min="17" max="17" width="16.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.375" style="63" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.875" style="49" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.875" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.875" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.375" style="63" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.875" style="49" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="8.875" style="49" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.875" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.125" style="63" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="18.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.75" style="49" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.625" style="49" customWidth="1"/>
+    <col min="19" max="19" width="38.5" style="49" customWidth="1"/>
+    <col min="20" max="20" width="16.375" style="63" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.875" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.875" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.375" style="63" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="8.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.875" style="61" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.125" style="63" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="18.625" style="49" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7.75" style="49" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.125" style="69" bestFit="1" customWidth="1"/>
-    <col min="36" max="38" width="14.125" style="49" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="18.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.125" style="49" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="18.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.375" style="70" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.375" style="71" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="10.875" style="71" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.75" style="71" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.25" style="71" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.375" style="71" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.875" style="49" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.875" style="60" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.875" style="61" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="8" style="63" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="16.5" style="50" customWidth="1"/>
-    <col min="56" max="57" width="19.25" style="51" customWidth="1"/>
-    <col min="58" max="58" width="21" style="51" customWidth="1"/>
+    <col min="35" max="35" width="11.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.125" style="69" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="14.125" style="49" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="18.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.125" style="49" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.375" style="70" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.375" style="71" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="10.875" style="71" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.75" style="71" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="24.25" style="71" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="15.375" style="71" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="17.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="6.875" style="49" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.875" style="60" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.875" style="61" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8" style="63" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16.5" style="50" customWidth="1"/>
+    <col min="58" max="59" width="19.25" style="51" customWidth="1"/>
+    <col min="60" max="60" width="21" style="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="47" customFormat="1" ht="14.25" thickBot="1">
+    <row r="1" spans="1:60" s="47" customFormat="1" ht="14.25" thickBot="1">
       <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
@@ -5336,27 +5346,27 @@
       <c r="O1" s="77"/>
       <c r="P1" s="77"/>
       <c r="Q1" s="77"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="79" t="s">
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
       <c r="V1" s="80"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="79" t="s">
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="Y1" s="80"/>
-      <c r="Z1" s="80"/>
       <c r="AA1" s="80"/>
       <c r="AB1" s="80"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="82" t="s">
+      <c r="AC1" s="80"/>
+      <c r="AD1" s="80"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="AE1" s="83"/>
-      <c r="AF1" s="83"/>
       <c r="AG1" s="83"/>
       <c r="AH1" s="83"/>
       <c r="AI1" s="83"/>
@@ -5373,22 +5383,24 @@
       <c r="AT1" s="83"/>
       <c r="AU1" s="83"/>
       <c r="AV1" s="83"/>
-      <c r="AW1" s="84"/>
-      <c r="AX1" s="82" t="s">
+      <c r="AW1" s="83"/>
+      <c r="AX1" s="83"/>
+      <c r="AY1" s="84"/>
+      <c r="AZ1" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="AY1" s="83"/>
-      <c r="AZ1" s="83"/>
       <c r="BA1" s="83"/>
       <c r="BB1" s="83"/>
-      <c r="BC1" s="66"/>
-      <c r="BD1" s="75" t="s">
+      <c r="BC1" s="83"/>
+      <c r="BD1" s="83"/>
+      <c r="BE1" s="66"/>
+      <c r="BF1" s="75" t="s">
         <v>406</v>
       </c>
-      <c r="BE1" s="75"/>
-      <c r="BF1" s="75"/>
-    </row>
-    <row r="2" spans="1:58" s="48" customFormat="1">
+      <c r="BG1" s="75"/>
+      <c r="BH1" s="75"/>
+    </row>
+    <row r="2" spans="1:60" s="48" customFormat="1">
       <c r="A2" s="52" t="s">
         <v>13</v>
       </c>
@@ -5440,149 +5452,155 @@
       <c r="Q2" s="59" t="s">
         <v>504</v>
       </c>
-      <c r="R2" s="53" t="s">
+      <c r="R2" s="59" t="s">
+        <v>950</v>
+      </c>
+      <c r="S2" s="59" t="s">
+        <v>951</v>
+      </c>
+      <c r="T2" s="53" t="s">
         <v>505</v>
       </c>
-      <c r="S2" s="59" t="s">
+      <c r="U2" s="59" t="s">
         <v>506</v>
       </c>
-      <c r="T2" s="59" t="s">
+      <c r="V2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="59" t="s">
+      <c r="W2" s="59" t="s">
         <v>507</v>
       </c>
-      <c r="V2" s="59" t="s">
+      <c r="X2" s="59" t="s">
         <v>508</v>
       </c>
-      <c r="W2" s="59" t="s">
+      <c r="Y2" s="59" t="s">
         <v>509</v>
       </c>
-      <c r="X2" s="59" t="s">
+      <c r="Z2" s="59" t="s">
         <v>506</v>
       </c>
-      <c r="Y2" s="59" t="s">
+      <c r="AA2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="Z2" s="59" t="s">
+      <c r="AB2" s="59" t="s">
         <v>501</v>
       </c>
-      <c r="AA2" s="59" t="s">
+      <c r="AC2" s="59" t="s">
         <v>502</v>
       </c>
-      <c r="AB2" s="64" t="s">
+      <c r="AD2" s="64" t="s">
         <v>508</v>
       </c>
-      <c r="AC2" s="65" t="s">
+      <c r="AE2" s="65" t="s">
         <v>510</v>
       </c>
-      <c r="AD2" s="67" t="s">
+      <c r="AF2" s="67" t="s">
         <v>511</v>
       </c>
-      <c r="AE2" s="67" t="s">
+      <c r="AG2" s="67" t="s">
         <v>512</v>
       </c>
-      <c r="AF2" s="67" t="s">
+      <c r="AH2" s="67" t="s">
         <v>513</v>
       </c>
-      <c r="AG2" s="67" t="s">
+      <c r="AI2" s="67" t="s">
         <v>514</v>
       </c>
-      <c r="AH2" s="67" t="s">
+      <c r="AJ2" s="67" t="s">
         <v>515</v>
       </c>
-      <c r="AI2" s="67" t="s">
+      <c r="AK2" s="67" t="s">
         <v>516</v>
       </c>
-      <c r="AJ2" s="67" t="s">
+      <c r="AL2" s="67" t="s">
         <v>517</v>
       </c>
-      <c r="AK2" s="67" t="s">
+      <c r="AM2" s="67" t="s">
         <v>518</v>
       </c>
-      <c r="AL2" s="67" t="s">
+      <c r="AN2" s="67" t="s">
         <v>519</v>
       </c>
-      <c r="AM2" s="67" t="s">
+      <c r="AO2" s="67" t="s">
         <v>520</v>
       </c>
-      <c r="AN2" s="67" t="s">
+      <c r="AP2" s="67" t="s">
         <v>521</v>
       </c>
-      <c r="AO2" s="67" t="s">
+      <c r="AQ2" s="67" t="s">
         <v>522</v>
       </c>
-      <c r="AP2" s="67" t="s">
+      <c r="AR2" s="67" t="s">
         <v>523</v>
       </c>
-      <c r="AQ2" s="67" t="s">
+      <c r="AS2" s="67" t="s">
         <v>524</v>
       </c>
-      <c r="AR2" s="67" t="s">
+      <c r="AT2" s="67" t="s">
         <v>525</v>
       </c>
-      <c r="AS2" s="67" t="s">
+      <c r="AU2" s="67" t="s">
         <v>526</v>
       </c>
-      <c r="AT2" s="67" t="s">
+      <c r="AV2" s="67" t="s">
         <v>527</v>
       </c>
-      <c r="AU2" s="67" t="s">
+      <c r="AW2" s="67" t="s">
         <v>528</v>
       </c>
-      <c r="AV2" s="67" t="s">
+      <c r="AX2" s="67" t="s">
         <v>529</v>
       </c>
-      <c r="AW2" s="67" t="s">
+      <c r="AY2" s="67" t="s">
         <v>530</v>
       </c>
-      <c r="AX2" s="59" t="s">
+      <c r="AZ2" s="59" t="s">
         <v>506</v>
       </c>
-      <c r="AY2" s="59" t="s">
+      <c r="BA2" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="AZ2" s="59" t="s">
+      <c r="BB2" s="59" t="s">
         <v>507</v>
       </c>
-      <c r="BA2" s="59" t="s">
+      <c r="BC2" s="59" t="s">
         <v>531</v>
       </c>
-      <c r="BB2" s="68" t="s">
+      <c r="BD2" s="68" t="s">
         <v>532</v>
       </c>
-      <c r="BC2" s="54" t="s">
+      <c r="BE2" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="BD2" s="55" t="s">
+      <c r="BF2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="BE2" s="55" t="s">
+      <c r="BG2" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="BF2" s="55" t="s">
+      <c r="BH2" s="55" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="F1:R1"/>
-    <mergeCell ref="S1:W1"/>
-    <mergeCell ref="X1:AC1"/>
-    <mergeCell ref="AD1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BF1:BH1"/>
+    <mergeCell ref="F1:T1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="AF1:AY1"/>
+    <mergeCell ref="AZ1:BD1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
-  <dataValidations count="40">
+  <dataValidations count="39">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="D2"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="Q3:Q65515 X2 S2 P2 Q1 AX2"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="Q3:Q65515 Z2 U2 P2 AZ2 Q1"/>
     <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不可为负，整数位不可超过13位，小数位不可超过2位" sqref="J1:J2">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值最大为5位整数" sqref="L1:M2 U1:U2 AZ1:AZ2">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值最大为5位整数" sqref="L1:M2 W1:W2 BB1:BB2">
       <formula1>0</formula1>
       <formula2>99999</formula2>
     </dataValidation>
@@ -5601,30 +5619,27 @@
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过13位，小数位不可超过2位" sqref="V1:V2 AB1:AB2 BA1:BA2">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过13位，小数位不可超过2位" sqref="X1:X2 AD1:AD2 BC1:BC2">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="W1:W2 AC1:AC2">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值整数位不可超过3位，小数位不可超过5位" sqref="Y1:Y2 AE1:AE2">
       <formula1>-999.99999</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过3位，小数位不可超过5位" sqref="BB1:BB2">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="输入值不能为负，整数位不可超过3位，小数位不可超过5位" sqref="BD1:BD2">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL1">
       <formula1>"01 结构性投资类,02 债券类,03 股票类,04 股权类,05 另类投资类,06 混合类,07 非标准化债权类,08 银行存款类,09 理财直接融资工具类,10 新增可投资资产类,11 代客境外投资类,12 公募基金类,13 衍生产品类,14 商品类,15 同业存单类,16 拆放同业及买入返售类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1 R3:R1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T1 T3:T1048576 F3:G65515 AR3:AR65515 S3:S1048576 S1 R1 R3:R1048576">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65501">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:G65515 AP3:AP65515">
-      <formula1>"01 是,02 否"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="最短剩余期限（天）输入值必须大于等于0且必须为n(5)格式。" sqref="M3:M1048576">
       <formula1>0</formula1>
@@ -5646,75 +5661,75 @@
       <formula1>0</formula1>
       <formula2>999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="资产收益率必须为n(8,5)格式。" sqref="W3:W1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="资产收益率必须为n(8,5)格式。" sqref="Y3:Y1048576">
       <formula1>-999.99999</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="资产价值输入值必须大于等于0且必须为n(15,2)格式。" sqref="AB3:AB1048576 V3:V1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="资产价值输入值必须大于等于0且必须为n(15,2)格式。" sqref="AD3:AD1048576 X3:X1048576">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="期限（天）输入值必须大于等于0且必须为n(5)格式。" sqref="AZ3:AZ1048576 U3:U1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="期限（天）输入值必须大于等于0且必须为n(5)格式。" sqref="BB3:BB1048576 W3:W1048576">
       <formula1>0</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="资产收益率%必须为n(8,5)格式。" sqref="AC3:AC65515">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="资产收益率%必须为n(8,5)格式。" sqref="AE3:AE65515">
       <formula1>-999.99999</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="利率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="BB3:BB1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="利率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="BD3:BD1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="负债规模输入值必须大于等于0且必须为n(15,2)格式。" sqref="BA3:BA65515">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="负债规模输入值必须大于等于0且必须为n(15,2)格式。" sqref="BC3:BC65515">
       <formula1>0</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最低收益率输入值必须为n(8,5)格式。" sqref="AR3:AR1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最低收益率输入值必须为n(8,5)格式。" sqref="AT3:AT1048576">
       <formula1>-999.99999</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ3:AJ65515">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL3:AL65515">
       <formula1>"20 固定收益类,21 权益类,22 商品及金融衍生品类,23 混合类"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="其他合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AW3:AW1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="其他合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AY3:AY1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="中介服务机构合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AV3:AV1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="中介服务机构合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AX3:AX1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="交易相关合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AU3:AU1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="交易相关合计费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AW3:AW1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="托管费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AT3:AT1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="托管费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AV3:AV1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="管理费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AS3:AS1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="管理费率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AU3:AU1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最高收益率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AQ3:AQ1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="预期最高收益率%输入值必须大于等于0且必须为n(8,5)格式。" sqref="AS3:AS1048576">
       <formula1>0</formula1>
       <formula2>999.99999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="委托投资金额输入值必须为n(15,2)格式。" sqref="AI3:AI65515">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="委托投资金额输入值必须为n(15,2)格式。" sqref="AK3:AK65515">
       <formula1>-9999999999999.99</formula1>
       <formula2>9999999999999.99</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE1 BE3:BE1048576">
-      <formula1>INDIRECT($BD$3)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG1 BG3:BG1048576">
+      <formula1>INDIRECT($BF$3)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF1 BF3:BF1048576">
-      <formula1>INDIRECT($BE$3)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH1 BH3:BH1048576">
+      <formula1>INDIRECT($BG$3)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C1 C3:C1048576">
       <formula1>"1201 票据类  ,1210 信用证,1601 贵金属类,1602 大宗商品类,1699 其他商品类资产,2301 字画类艺术品,2302 古董类艺术品,2303 其他类艺术品,2304 影视等知识产权,2305 酒,1603 其他另类资产,2801 协议委外-银行,2802 协议委外-信托公司,2803 协议委外-证券公司,2804 协议委外-基金公司,2805 协议委外-期货公司,2806 协议委外-保险公司,2899 协议委外-其他,2000 其他(负债)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1 AO3:AO1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ1 AQ3:AQ1048576">
       <formula1>"01 集合管理,02 单独管理,99 其他"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5726,7 +5741,7 @@
           <x14:formula1>
             <xm:f>枚举值!$A$7:$M$7</xm:f>
           </x14:formula1>
-          <xm:sqref>BD3:BD1048576</xm:sqref>
+          <xm:sqref>BF3:BF1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -5744,13 +5759,13 @@
           <x14:formula1>
             <xm:f>国家或区域填写规则!$A$1:$A$239</xm:f>
           </x14:formula1>
-          <xm:sqref>S1 S3:S1048576 X1 X3:X1048576 AX1 AX3:AX1048576</xm:sqref>
+          <xm:sqref>U1 U3:U1048576 Z1 Z3:Z1048576 AZ1 AZ3:AZ1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
           </x14:formula1>
-          <xm:sqref>AL1 AL3:AL1048576</xm:sqref>
+          <xm:sqref>AN1 AN3:AN1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5820,13 +5835,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="86"/>
+      <c r="B1" s="104"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="94" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5834,25 +5849,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="98"/>
+      <c r="A3" s="95"/>
       <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="98"/>
+      <c r="A4" s="95"/>
       <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="99"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="97" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5860,13 +5875,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="101"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="99" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5874,13 +5889,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="101"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="100" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5888,61 +5903,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="103"/>
+      <c r="A11" s="101"/>
       <c r="B11" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="103"/>
+      <c r="A12" s="101"/>
       <c r="B12" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="103"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="103"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="103"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="103"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="103"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="103"/>
+      <c r="A18" s="101"/>
       <c r="B18" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="103"/>
+      <c r="A19" s="101"/>
       <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="103"/>
+      <c r="A20" s="101"/>
       <c r="B20" s="15" t="s">
         <v>53</v>
       </c>
@@ -5956,7 +5971,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="100" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5964,19 +5979,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="103"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="91"/>
+      <c r="A24" s="102"/>
       <c r="B24" s="13" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="100" t="s">
         <v>60</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5984,67 +5999,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="103"/>
+      <c r="A26" s="101"/>
       <c r="B26" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="103"/>
+      <c r="A27" s="101"/>
       <c r="B27" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="103"/>
+      <c r="A28" s="101"/>
       <c r="B28" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="103"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="103"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="103"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="103"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="103"/>
+      <c r="A33" s="101"/>
       <c r="B33" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="103"/>
+      <c r="A34" s="101"/>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="91"/>
+      <c r="A35" s="102"/>
       <c r="B35" s="30" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="100" t="s">
         <v>72</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -6052,25 +6067,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="103"/>
+      <c r="A37" s="101"/>
       <c r="B37" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="103"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="91"/>
+      <c r="A39" s="102"/>
       <c r="B39" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="90" t="s">
+      <c r="A40" s="100" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -6078,43 +6093,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="103"/>
+      <c r="A41" s="101"/>
       <c r="B41" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="103"/>
+      <c r="A42" s="101"/>
       <c r="B42" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="103"/>
+      <c r="A43" s="101"/>
       <c r="B43" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="103"/>
+      <c r="A44" s="101"/>
       <c r="B44" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="103"/>
+      <c r="A45" s="101"/>
       <c r="B45" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="91"/>
+      <c r="A46" s="102"/>
       <c r="B46" s="13" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="90" t="s">
+      <c r="A47" s="100" t="s">
         <v>85</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -6122,61 +6137,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="103"/>
+      <c r="A48" s="101"/>
       <c r="B48" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="103"/>
+      <c r="A49" s="101"/>
       <c r="B49" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="103"/>
+      <c r="A50" s="101"/>
       <c r="B50" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="103"/>
+      <c r="A51" s="101"/>
       <c r="B51" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="103"/>
+      <c r="A52" s="101"/>
       <c r="B52" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="103"/>
+      <c r="A53" s="101"/>
       <c r="B53" s="15" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="103"/>
+      <c r="A54" s="101"/>
       <c r="B54" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="103"/>
+      <c r="A55" s="101"/>
       <c r="B55" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="91"/>
+      <c r="A56" s="102"/>
       <c r="B56" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="90" t="s">
+      <c r="A57" s="100" t="s">
         <v>96</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -6184,19 +6199,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="103"/>
+      <c r="A58" s="101"/>
       <c r="B58" s="10" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="91"/>
+      <c r="A59" s="102"/>
       <c r="B59" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="90" t="s">
+      <c r="A60" s="100" t="s">
         <v>100</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -6204,37 +6219,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="103"/>
+      <c r="A61" s="101"/>
       <c r="B61" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="103"/>
+      <c r="A62" s="101"/>
       <c r="B62" s="24" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="103"/>
+      <c r="A63" s="101"/>
       <c r="B63" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="103"/>
+      <c r="A64" s="101"/>
       <c r="B64" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="91"/>
+      <c r="A65" s="102"/>
       <c r="B65" s="17" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="90" t="s">
+      <c r="A66" s="100" t="s">
         <v>107</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -6242,37 +6257,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="103"/>
+      <c r="A67" s="101"/>
       <c r="B67" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="103"/>
+      <c r="A68" s="101"/>
       <c r="B68" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="103"/>
+      <c r="A69" s="101"/>
       <c r="B69" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="103"/>
+      <c r="A70" s="101"/>
       <c r="B70" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="91"/>
+      <c r="A71" s="102"/>
       <c r="B71" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="90" t="s">
+      <c r="A72" s="100" t="s">
         <v>114</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6280,103 +6295,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="103"/>
+      <c r="A73" s="101"/>
       <c r="B73" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="103"/>
+      <c r="A74" s="101"/>
       <c r="B74" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="103"/>
+      <c r="A75" s="101"/>
       <c r="B75" s="10" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="103"/>
+      <c r="A76" s="101"/>
       <c r="B76" s="10" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="103"/>
+      <c r="A77" s="101"/>
       <c r="B77" s="25" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="103"/>
+      <c r="A78" s="101"/>
       <c r="B78" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="103"/>
+      <c r="A79" s="101"/>
       <c r="B79" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="103"/>
+      <c r="A80" s="101"/>
       <c r="B80" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="103"/>
+      <c r="A81" s="101"/>
       <c r="B81" s="25" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="103"/>
+      <c r="A82" s="101"/>
       <c r="B82" s="10" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="103"/>
+      <c r="A83" s="101"/>
       <c r="B83" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="103"/>
+      <c r="A84" s="101"/>
       <c r="B84" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="103"/>
+      <c r="A85" s="101"/>
       <c r="B85" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="103"/>
+      <c r="A86" s="101"/>
       <c r="B86" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="103"/>
+      <c r="A87" s="101"/>
       <c r="B87" s="25" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="91"/>
+      <c r="A88" s="102"/>
       <c r="B88" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="90" t="s">
+      <c r="A89" s="100" t="s">
         <v>132</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6384,38 +6399,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="103"/>
+      <c r="A90" s="101"/>
       <c r="B90" s="15" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="103"/>
+      <c r="A91" s="101"/>
       <c r="B91" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="103"/>
+      <c r="A92" s="101"/>
       <c r="B92" s="32" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="103"/>
+      <c r="A93" s="101"/>
       <c r="B93" s="15" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="91"/>
+      <c r="A94" s="102"/>
       <c r="B94" s="13" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="90" t="s">
+      <c r="A95" s="100" t="s">
         <v>139</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6423,43 +6438,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="103"/>
+      <c r="A96" s="101"/>
       <c r="B96" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="103"/>
+      <c r="A97" s="101"/>
       <c r="B97" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="103"/>
+      <c r="A98" s="101"/>
       <c r="B98" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="103"/>
+      <c r="A99" s="101"/>
       <c r="B99" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="103"/>
+      <c r="A100" s="101"/>
       <c r="B100" s="25" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="91"/>
+      <c r="A101" s="102"/>
       <c r="B101" s="21" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="90" t="s">
+      <c r="A102" s="100" t="s">
         <v>147</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6467,7 +6482,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="91"/>
+      <c r="A103" s="102"/>
       <c r="B103" s="13" t="s">
         <v>149</v>
       </c>
@@ -6485,10 +6500,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="85" t="s">
+      <c r="A107" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="B107" s="86"/>
+      <c r="B107" s="104"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6659,17 +6674,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="104" t="s">
+      <c r="A137" s="88" t="s">
         <v>181</v>
       </c>
-      <c r="B137" s="105"/>
+      <c r="B137" s="89"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="106"/>
-      <c r="B138" s="107"/>
+      <c r="A138" s="90"/>
+      <c r="B138" s="91"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="92" t="s">
+      <c r="A139" s="85" t="s">
         <v>182</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6677,31 +6692,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="93"/>
+      <c r="A140" s="86"/>
       <c r="B140" s="39" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="93"/>
+      <c r="A141" s="86"/>
       <c r="B141" s="39" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="93"/>
+      <c r="A142" s="86"/>
       <c r="B142" s="39" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="94"/>
+      <c r="A143" s="87"/>
       <c r="B143" s="41" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="92" t="s">
+      <c r="A144" s="85" t="s">
         <v>188</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6709,43 +6724,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="93"/>
+      <c r="A145" s="86"/>
       <c r="B145" s="39" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="93"/>
+      <c r="A146" s="86"/>
       <c r="B146" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="93"/>
+      <c r="A147" s="86"/>
       <c r="B147" s="39" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="93"/>
+      <c r="A148" s="86"/>
       <c r="B148" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="93"/>
+      <c r="A149" s="86"/>
       <c r="B149" s="39" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="94"/>
+      <c r="A150" s="87"/>
       <c r="B150" s="41" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="92" t="s">
+      <c r="A151" s="85" t="s">
         <v>196</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6753,187 +6768,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="93"/>
+      <c r="A152" s="86"/>
       <c r="B152" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="93"/>
+      <c r="A153" s="86"/>
       <c r="B153" s="39" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="93"/>
+      <c r="A154" s="86"/>
       <c r="B154" s="39" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="93"/>
+      <c r="A155" s="86"/>
       <c r="B155" s="39" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="93"/>
+      <c r="A156" s="86"/>
       <c r="B156" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="93"/>
+      <c r="A157" s="86"/>
       <c r="B157" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="93"/>
+      <c r="A158" s="86"/>
       <c r="B158" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="93"/>
+      <c r="A159" s="86"/>
       <c r="B159" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="93"/>
+      <c r="A160" s="86"/>
       <c r="B160" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="93"/>
+      <c r="A161" s="86"/>
       <c r="B161" s="39" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="93"/>
+      <c r="A162" s="86"/>
       <c r="B162" s="39" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="93"/>
+      <c r="A163" s="86"/>
       <c r="B163" s="39" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="93"/>
+      <c r="A164" s="86"/>
       <c r="B164" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="93"/>
+      <c r="A165" s="86"/>
       <c r="B165" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="93"/>
+      <c r="A166" s="86"/>
       <c r="B166" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="93"/>
+      <c r="A167" s="86"/>
       <c r="B167" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="93"/>
+      <c r="A168" s="86"/>
       <c r="B168" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="93"/>
+      <c r="A169" s="86"/>
       <c r="B169" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="93"/>
+      <c r="A170" s="86"/>
       <c r="B170" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="93"/>
+      <c r="A171" s="86"/>
       <c r="B171" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="93"/>
+      <c r="A172" s="86"/>
       <c r="B172" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="93"/>
+      <c r="A173" s="86"/>
       <c r="B173" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="93"/>
+      <c r="A174" s="86"/>
       <c r="B174" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="93"/>
+      <c r="A175" s="86"/>
       <c r="B175" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="93"/>
+      <c r="A176" s="86"/>
       <c r="B176" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="93"/>
+      <c r="A177" s="86"/>
       <c r="B177" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="93"/>
+      <c r="A178" s="86"/>
       <c r="B178" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="93"/>
+      <c r="A179" s="86"/>
       <c r="B179" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="93"/>
+      <c r="A180" s="86"/>
       <c r="B180" s="39" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="94"/>
+      <c r="A181" s="87"/>
       <c r="B181" s="41" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="92" t="s">
+      <c r="A182" s="85" t="s">
         <v>228</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6941,19 +6956,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="93"/>
+      <c r="A183" s="86"/>
       <c r="B183" s="39" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="94"/>
+      <c r="A184" s="87"/>
       <c r="B184" s="41" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="92" t="s">
+      <c r="A185" s="85" t="s">
         <v>232</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6961,25 +6976,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="93"/>
+      <c r="A186" s="86"/>
       <c r="B186" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="93"/>
+      <c r="A187" s="86"/>
       <c r="B187" s="39" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="94"/>
+      <c r="A188" s="87"/>
       <c r="B188" s="41" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="92" t="s">
+      <c r="A189" s="85" t="s">
         <v>237</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6987,13 +7002,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="94"/>
+      <c r="A190" s="87"/>
       <c r="B190" s="41" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="92" t="s">
+      <c r="A191" s="85" t="s">
         <v>240</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -7001,49 +7016,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="93"/>
+      <c r="A192" s="86"/>
       <c r="B192" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="93"/>
+      <c r="A193" s="86"/>
       <c r="B193" s="39" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="93"/>
+      <c r="A194" s="86"/>
       <c r="B194" s="39" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="93"/>
+      <c r="A195" s="86"/>
       <c r="B195" s="39" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="93"/>
+      <c r="A196" s="86"/>
       <c r="B196" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="93"/>
+      <c r="A197" s="86"/>
       <c r="B197" s="39" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="94"/>
+      <c r="A198" s="87"/>
       <c r="B198" s="41" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="92" t="s">
+      <c r="A199" s="85" t="s">
         <v>249</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -7051,13 +7066,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="94"/>
+      <c r="A200" s="87"/>
       <c r="B200" s="41" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="92" t="s">
+      <c r="A201" s="85" t="s">
         <v>252</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -7065,19 +7080,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="93"/>
+      <c r="A202" s="86"/>
       <c r="B202" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="94"/>
+      <c r="A203" s="87"/>
       <c r="B203" s="41" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="92" t="s">
+      <c r="A204" s="85" t="s">
         <v>256</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -7085,19 +7100,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="93"/>
+      <c r="A205" s="86"/>
       <c r="B205" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="93"/>
+      <c r="A206" s="86"/>
       <c r="B206" s="39" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="94"/>
+      <c r="A207" s="87"/>
       <c r="B207" s="41" t="s">
         <v>260</v>
       </c>
@@ -7111,7 +7126,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="92" t="s">
+      <c r="A209" s="85" t="s">
         <v>263</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -7119,13 +7134,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="94"/>
+      <c r="A210" s="87"/>
       <c r="B210" s="41" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="92" t="s">
+      <c r="A211" s="85" t="s">
         <v>266</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -7133,19 +7148,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="93"/>
+      <c r="A212" s="86"/>
       <c r="B212" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="94"/>
+      <c r="A213" s="87"/>
       <c r="B213" s="41" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="92" t="s">
+      <c r="A214" s="85" t="s">
         <v>270</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -7153,19 +7168,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="93"/>
+      <c r="A215" s="86"/>
       <c r="B215" s="39" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="94"/>
+      <c r="A216" s="87"/>
       <c r="B216" s="41" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="92" t="s">
+      <c r="A217" s="85" t="s">
         <v>274</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -7173,13 +7188,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="93"/>
+      <c r="A218" s="86"/>
       <c r="B218" s="39" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="94"/>
+      <c r="A219" s="87"/>
       <c r="B219" s="41" t="s">
         <v>277</v>
       </c>
@@ -7193,7 +7208,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="92" t="s">
+      <c r="A221" s="85" t="s">
         <v>280</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -7201,13 +7216,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="94"/>
+      <c r="A222" s="87"/>
       <c r="B222" s="41" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="92" t="s">
+      <c r="A223" s="85" t="s">
         <v>283</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -7215,31 +7230,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="93"/>
+      <c r="A224" s="86"/>
       <c r="B224" s="39" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="93"/>
+      <c r="A225" s="86"/>
       <c r="B225" s="39" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="93"/>
+      <c r="A226" s="86"/>
       <c r="B226" s="39" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="94"/>
+      <c r="A227" s="87"/>
       <c r="B227" s="41" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="92" t="s">
+      <c r="A228" s="85" t="s">
         <v>289</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7247,31 +7262,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="93"/>
+      <c r="A229" s="86"/>
       <c r="B229" s="39" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="93"/>
+      <c r="A230" s="86"/>
       <c r="B230" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="93"/>
+      <c r="A231" s="86"/>
       <c r="B231" s="39" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="93"/>
+      <c r="A232" s="86"/>
       <c r="B232" s="39" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="94"/>
+      <c r="A233" s="87"/>
       <c r="B233" s="41" t="s">
         <v>295</v>
       </c>
@@ -7285,16 +7300,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="87" t="s">
+      <c r="A236" s="105" t="s">
         <v>298</v>
       </c>
-      <c r="B236" s="86"/>
+      <c r="B236" s="104"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="85" t="s">
+      <c r="A239" s="103" t="s">
         <v>299</v>
       </c>
-      <c r="B239" s="86"/>
+      <c r="B239" s="104"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7393,10 +7408,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="88" t="s">
+      <c r="A257" s="106" t="s">
         <v>316</v>
       </c>
-      <c r="B257" s="89"/>
+      <c r="B257" s="107"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7573,10 +7588,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="95" t="s">
+      <c r="A288" s="92" t="s">
         <v>346</v>
       </c>
-      <c r="B288" s="96"/>
+      <c r="B288" s="93"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7767,14 +7782,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7791,22 +7814,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7826,10 +7841,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="117" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="109"/>
+      <c r="B1" s="118"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7843,7 +7858,7 @@
       <c r="A3" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="111" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7851,25 +7866,25 @@
       <c r="A4" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="111"/>
+      <c r="B4" s="112"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="111"/>
+      <c r="B5" s="112"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="112"/>
+      <c r="B6" s="113"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="111" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7877,25 +7892,25 @@
       <c r="A8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="111"/>
+      <c r="B8" s="112"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="111"/>
+      <c r="B9" s="112"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="112"/>
+      <c r="B10" s="113"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="111" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7903,85 +7918,85 @@
       <c r="A12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="111"/>
+      <c r="B12" s="112"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="111"/>
+      <c r="B13" s="112"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="111"/>
+      <c r="B14" s="112"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="111"/>
+      <c r="B15" s="112"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="111"/>
+      <c r="B16" s="112"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="111"/>
+      <c r="B17" s="112"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="B18" s="111"/>
+      <c r="B18" s="112"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="111"/>
+      <c r="B19" s="112"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="B20" s="111"/>
+      <c r="B20" s="112"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="B21" s="111"/>
+      <c r="B21" s="112"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="111"/>
+      <c r="B22" s="112"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="113"/>
+      <c r="B23" s="119"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="114"/>
+      <c r="B24" s="120"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="111" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7989,61 +8004,61 @@
       <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="111"/>
+      <c r="B26" s="112"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="111"/>
+      <c r="B27" s="112"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="111"/>
+      <c r="B28" s="112"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="111"/>
+      <c r="B29" s="112"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B30" s="111"/>
+      <c r="B30" s="112"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="111"/>
+      <c r="B31" s="112"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="B32" s="111"/>
+      <c r="B32" s="112"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B33" s="111"/>
+      <c r="B33" s="112"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="112"/>
+      <c r="B34" s="113"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="B35" s="110" t="s">
+      <c r="B35" s="111" t="s">
         <v>392</v>
       </c>
     </row>
@@ -8051,13 +8066,13 @@
       <c r="A36" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B36" s="112"/>
+      <c r="B36" s="113"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="110" t="s">
+      <c r="B37" s="111" t="s">
         <v>4</v>
       </c>
     </row>
@@ -8065,19 +8080,19 @@
       <c r="A38" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="111"/>
+      <c r="B38" s="112"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="111"/>
+      <c r="B39" s="112"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="B40" s="110" t="s">
+      <c r="B40" s="111" t="s">
         <v>395</v>
       </c>
     </row>
@@ -8085,37 +8100,37 @@
       <c r="A41" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B41" s="111"/>
+      <c r="B41" s="112"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="111"/>
+      <c r="B42" s="112"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B43" s="111"/>
+      <c r="B43" s="112"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="B44" s="111"/>
+      <c r="B44" s="112"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="111"/>
+      <c r="B45" s="112"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="112"/>
+      <c r="B46" s="113"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -8129,7 +8144,7 @@
       <c r="A48" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="110" t="s">
+      <c r="B48" s="111" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8137,13 +8152,13 @@
       <c r="A49" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="112"/>
+      <c r="B49" s="113"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="110" t="s">
+      <c r="B50" s="111" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8151,25 +8166,25 @@
       <c r="A51" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="111"/>
+      <c r="B51" s="112"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B52" s="111"/>
+      <c r="B52" s="112"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="111"/>
+      <c r="B53" s="112"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="112"/>
+      <c r="B54" s="113"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -8183,7 +8198,7 @@
       <c r="A56" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B56" s="110" t="s">
+      <c r="B56" s="111" t="s">
         <v>8</v>
       </c>
     </row>
@@ -8191,19 +8206,19 @@
       <c r="A57" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="111"/>
+      <c r="B57" s="112"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="112"/>
+      <c r="B58" s="113"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B59" s="110" t="s">
+      <c r="B59" s="111" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8211,37 +8226,37 @@
       <c r="A60" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="111"/>
+      <c r="B60" s="112"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="111"/>
+      <c r="B61" s="112"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="111"/>
+      <c r="B62" s="112"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="111"/>
+      <c r="B63" s="112"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="B64" s="112"/>
+      <c r="B64" s="113"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B65" s="118" t="s">
+      <c r="B65" s="114" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8249,26 +8264,26 @@
       <c r="A66" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B66" s="119"/>
+      <c r="B66" s="115"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B67" s="119"/>
+      <c r="B67" s="115"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B68" s="120"/>
+      <c r="B68" s="116"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="110" t="s">
+      <c r="B69" s="111" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8276,37 +8291,37 @@
       <c r="A70" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B70" s="111"/>
+      <c r="B70" s="112"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B71" s="111"/>
+      <c r="B71" s="112"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B72" s="111"/>
+      <c r="B72" s="112"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B73" s="111"/>
+      <c r="B73" s="112"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B74" s="112"/>
+      <c r="B74" s="113"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B75" s="110" t="s">
+      <c r="B75" s="111" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8314,139 +8329,139 @@
       <c r="A76" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B76" s="111"/>
+      <c r="B76" s="112"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="111"/>
+      <c r="B77" s="112"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B78" s="111"/>
+      <c r="B78" s="112"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B79" s="111"/>
+      <c r="B79" s="112"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B80" s="111"/>
+      <c r="B80" s="112"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B81" s="111"/>
+      <c r="B81" s="112"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B82" s="111"/>
+      <c r="B82" s="112"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B83" s="111"/>
+      <c r="B83" s="112"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="111"/>
+      <c r="B84" s="112"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B85" s="111"/>
+      <c r="B85" s="112"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B86" s="111"/>
+      <c r="B86" s="112"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B87" s="111"/>
+      <c r="B87" s="112"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="111"/>
+      <c r="B88" s="112"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B89" s="111"/>
+      <c r="B89" s="112"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B90" s="111"/>
+      <c r="B90" s="112"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B91" s="111"/>
+      <c r="B91" s="112"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B92" s="111"/>
+      <c r="B92" s="112"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B93" s="111"/>
+      <c r="B93" s="112"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="111"/>
+      <c r="B94" s="112"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B95" s="111"/>
+      <c r="B95" s="112"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B96" s="111"/>
+      <c r="B96" s="112"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="111"/>
+      <c r="B97" s="112"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="B98" s="115" t="s">
+      <c r="B98" s="108" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8454,37 +8469,37 @@
       <c r="A99" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B99" s="116"/>
+      <c r="B99" s="109"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B100" s="116"/>
+      <c r="B100" s="109"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B101" s="116"/>
+      <c r="B101" s="109"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B102" s="116"/>
+      <c r="B102" s="109"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B103" s="116"/>
+      <c r="B103" s="109"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B104" s="117"/>
+      <c r="B104" s="110"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8496,22 +8511,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
